--- a/diseases/d192/2026-2029.xlsx
+++ b/diseases/d192/2026-2029.xlsx
@@ -1086,6 +1086,792 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>D192</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>work-related-repetitive-strain-injury</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Work-related repetitive strain injury</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>D192</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Work-related repetitive strain injury</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>职业相关重复性劳损</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>1253</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1253</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.5867130339468767</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>SER_BR_LERD</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>SER_BR_LERD</t>
+        </is>
+      </c>
+      <c r="AT4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>D192</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>work-related-repetitive-strain-injury</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Work-related repetitive strain injury</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>D192</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Work-related repetitive strain injury</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>职业相关重复性劳损</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>1253</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1253</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>SER_BR_LERD</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>SER_BR_LERD</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>SRC_BR_SINAN</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Work-related repetitive strain injury</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>country:BR:national</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>SINAN LERD work-related repetitive strain injury or musculoskeletal disorder notifications; LER is retained as the historical source code alias.</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>final; provisional</t>
+        </is>
+      </c>
+      <c r="AN5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>SER_BR_LERD</t>
+        </is>
+      </c>
+      <c r="AT5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>D192</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>work-related-repetitive-strain-injury</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Work-related repetitive strain injury</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>D192</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Work-related repetitive strain injury</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>职业相关重复性劳损</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>391</v>
+      </c>
+      <c r="O6" t="n">
+        <v>391</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.1830844343760804</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>SER_BR_LERD</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>SER_BR_LERD</t>
+        </is>
+      </c>
+      <c r="AT6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>D192</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>work-related-repetitive-strain-injury</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Work-related repetitive strain injury</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>D192</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Work-related repetitive strain injury</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>职业相关重复性劳损</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>391</v>
+      </c>
+      <c r="O7" t="n">
+        <v>391</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>SER_BR_LERD</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>SER_BR_LERD</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>SRC_BR_SINAN</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Work-related repetitive strain injury</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>country:BR:national</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>SINAN LERD work-related repetitive strain injury or musculoskeletal disorder notifications; LER is retained as the historical source code alias.</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>final; provisional</t>
+        </is>
+      </c>
+      <c r="AN7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>SER_BR_LERD</t>
+        </is>
+      </c>
+      <c r="AT7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1119,7 +1905,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
@@ -1202,7 +1988,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -1212,7 +1998,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -1232,7 +2018,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -1264,7 +2050,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>547</v>
+        <v>2191</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d192/2026-2029.xlsx
+++ b/diseases/d192/2026-2029.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">

--- a/diseases/d192/2026-2029.xlsx
+++ b/diseases/d192/2026-2029.xlsx
@@ -992,7 +992,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3617,7 +3617,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -3992,7 +3992,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4367,7 +4367,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5117,7 +5117,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5492,7 +5492,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -5867,7 +5867,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6242,7 +6242,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6617,7 +6617,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -6992,7 +6992,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7367,7 +7367,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8117,7 +8117,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8492,7 +8492,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -8867,7 +8867,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -9617,7 +9617,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -9992,7 +9992,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10367,7 +10367,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -10742,7 +10742,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11117,7 +11117,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11492,7 +11492,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -11867,7 +11867,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12242,7 +12242,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -12617,7 +12617,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -12992,7 +12992,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -13367,7 +13367,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -13742,7 +13742,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14117,7 +14117,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -14492,7 +14492,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -14867,7 +14867,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -15242,7 +15242,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -15992,7 +15992,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -16367,7 +16367,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -16742,7 +16742,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -17117,7 +17117,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -17492,7 +17492,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -17867,7 +17867,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -18242,7 +18242,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -18617,7 +18617,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -18992,7 +18992,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -19367,7 +19367,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -19742,7 +19742,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -20117,7 +20117,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -20492,7 +20492,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -20867,7 +20867,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -21242,7 +21242,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -21617,7 +21617,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -21992,7 +21992,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -22367,7 +22367,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -22742,7 +22742,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -23117,7 +23117,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -23492,7 +23492,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -23867,7 +23867,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -24242,7 +24242,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -24617,7 +24617,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -24992,7 +24992,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -25367,7 +25367,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -25742,7 +25742,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -26117,7 +26117,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -26492,7 +26492,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -26867,7 +26867,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -27242,7 +27242,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -27617,7 +27617,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -27992,7 +27992,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -28367,7 +28367,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -28742,7 +28742,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -29117,7 +29117,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -29492,7 +29492,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -29867,7 +29867,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -30242,7 +30242,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -30617,7 +30617,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -30992,7 +30992,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -31367,7 +31367,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -31742,7 +31742,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -32117,7 +32117,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -32492,7 +32492,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -32867,7 +32867,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -33242,7 +33242,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -33617,7 +33617,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -33992,7 +33992,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -34367,7 +34367,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -34742,7 +34742,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -35117,7 +35117,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -35492,7 +35492,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -35867,7 +35867,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -36242,7 +36242,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -36617,7 +36617,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
@@ -36992,7 +36992,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -37367,7 +37367,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK197" t="inlineStr">
@@ -37742,7 +37742,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -38117,7 +38117,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -38492,7 +38492,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -38867,7 +38867,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -39242,7 +39242,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -39617,7 +39617,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -39992,7 +39992,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -40367,7 +40367,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -40742,7 +40742,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -41117,7 +41117,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -41501,7 +41501,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -41885,7 +41885,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
@@ -42260,7 +42260,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -42635,7 +42635,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -43010,7 +43010,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -43385,7 +43385,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -43760,7 +43760,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -44135,7 +44135,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -44510,7 +44510,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -44885,7 +44885,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -45260,7 +45260,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
@@ -45635,7 +45635,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">
@@ -46010,7 +46010,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -46385,7 +46385,7 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
@@ -46760,7 +46760,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -47135,7 +47135,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -47510,7 +47510,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -47885,7 +47885,7 @@
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">
@@ -48260,7 +48260,7 @@
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
@@ -48635,7 +48635,7 @@
       </c>
       <c r="AJ257" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK257" t="inlineStr">
@@ -49010,7 +49010,7 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
@@ -49385,7 +49385,7 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
@@ -49760,7 +49760,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -50135,7 +50135,7 @@
       </c>
       <c r="AJ265" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK265" t="inlineStr">
@@ -50510,7 +50510,7 @@
       </c>
       <c r="AJ267" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK267" t="inlineStr">
@@ -50885,7 +50885,7 @@
       </c>
       <c r="AJ269" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK269" t="inlineStr">
@@ -51260,7 +51260,7 @@
       </c>
       <c r="AJ271" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK271" t="inlineStr">
@@ -51635,7 +51635,7 @@
       </c>
       <c r="AJ273" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK273" t="inlineStr">
@@ -52010,7 +52010,7 @@
       </c>
       <c r="AJ275" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK275" t="inlineStr">
@@ -52385,7 +52385,7 @@
       </c>
       <c r="AJ277" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK277" t="inlineStr">
@@ -52760,7 +52760,7 @@
       </c>
       <c r="AJ279" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK279" t="inlineStr">
@@ -53135,7 +53135,7 @@
       </c>
       <c r="AJ281" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK281" t="inlineStr">
@@ -53510,7 +53510,7 @@
       </c>
       <c r="AJ283" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr">
@@ -53885,7 +53885,7 @@
       </c>
       <c r="AJ285" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK285" t="inlineStr">
@@ -54260,7 +54260,7 @@
       </c>
       <c r="AJ287" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK287" t="inlineStr">
@@ -54635,7 +54635,7 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">
@@ -55010,7 +55010,7 @@
       </c>
       <c r="AJ291" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK291" t="inlineStr">
@@ -55385,7 +55385,7 @@
       </c>
       <c r="AJ293" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK293" t="inlineStr">
@@ -55760,7 +55760,7 @@
       </c>
       <c r="AJ295" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK295" t="inlineStr">
@@ -56135,7 +56135,7 @@
       </c>
       <c r="AJ297" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK297" t="inlineStr">
@@ -56510,7 +56510,7 @@
       </c>
       <c r="AJ299" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK299" t="inlineStr">
@@ -56885,7 +56885,7 @@
       </c>
       <c r="AJ301" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK301" t="inlineStr">
@@ -57260,7 +57260,7 @@
       </c>
       <c r="AJ303" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK303" t="inlineStr">
@@ -57635,7 +57635,7 @@
       </c>
       <c r="AJ305" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK305" t="inlineStr">
@@ -58010,7 +58010,7 @@
       </c>
       <c r="AJ307" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK307" t="inlineStr">
@@ -58385,7 +58385,7 @@
       </c>
       <c r="AJ309" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK309" t="inlineStr">
@@ -58760,7 +58760,7 @@
       </c>
       <c r="AJ311" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK311" t="inlineStr">
@@ -59135,7 +59135,7 @@
       </c>
       <c r="AJ313" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK313" t="inlineStr">
@@ -59510,7 +59510,7 @@
       </c>
       <c r="AJ315" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK315" t="inlineStr">
@@ -59885,7 +59885,7 @@
       </c>
       <c r="AJ317" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK317" t="inlineStr">
@@ -60260,7 +60260,7 @@
       </c>
       <c r="AJ319" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK319" t="inlineStr">
@@ -60635,7 +60635,7 @@
       </c>
       <c r="AJ321" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK321" t="inlineStr">
@@ -61010,7 +61010,7 @@
       </c>
       <c r="AJ323" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK323" t="inlineStr">
@@ -61385,7 +61385,7 @@
       </c>
       <c r="AJ325" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK325" t="inlineStr">
@@ -61760,7 +61760,7 @@
       </c>
       <c r="AJ327" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK327" t="inlineStr">
@@ -62144,7 +62144,7 @@
       </c>
       <c r="AJ329" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK329" t="inlineStr">
@@ -62528,7 +62528,7 @@
       </c>
       <c r="AJ331" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK331" t="inlineStr">
@@ -62903,7 +62903,7 @@
       </c>
       <c r="AJ333" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK333" t="inlineStr">
@@ -63278,7 +63278,7 @@
       </c>
       <c r="AJ335" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK335" t="inlineStr">
@@ -63653,7 +63653,7 @@
       </c>
       <c r="AJ337" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK337" t="inlineStr">
@@ -64028,7 +64028,7 @@
       </c>
       <c r="AJ339" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK339" t="inlineStr">
@@ -64403,7 +64403,7 @@
       </c>
       <c r="AJ341" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK341" t="inlineStr">
@@ -64778,7 +64778,7 @@
       </c>
       <c r="AJ343" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK343" t="inlineStr">
@@ -65153,7 +65153,7 @@
       </c>
       <c r="AJ345" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK345" t="inlineStr">
@@ -65528,7 +65528,7 @@
       </c>
       <c r="AJ347" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK347" t="inlineStr">
@@ -65903,7 +65903,7 @@
       </c>
       <c r="AJ349" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK349" t="inlineStr">
@@ -66278,7 +66278,7 @@
       </c>
       <c r="AJ351" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK351" t="inlineStr">
@@ -66653,7 +66653,7 @@
       </c>
       <c r="AJ353" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK353" t="inlineStr">
@@ -67028,7 +67028,7 @@
       </c>
       <c r="AJ355" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK355" t="inlineStr">
@@ -67403,7 +67403,7 @@
       </c>
       <c r="AJ357" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK357" t="inlineStr">
@@ -67778,7 +67778,7 @@
       </c>
       <c r="AJ359" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK359" t="inlineStr">
@@ -68153,7 +68153,7 @@
       </c>
       <c r="AJ361" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK361" t="inlineStr">
@@ -68528,7 +68528,7 @@
       </c>
       <c r="AJ363" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK363" t="inlineStr">
@@ -68903,7 +68903,7 @@
       </c>
       <c r="AJ365" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK365" t="inlineStr">
@@ -69278,7 +69278,7 @@
       </c>
       <c r="AJ367" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK367" t="inlineStr">
@@ -69653,7 +69653,7 @@
       </c>
       <c r="AJ369" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK369" t="inlineStr">
@@ -70028,7 +70028,7 @@
       </c>
       <c r="AJ371" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK371" t="inlineStr">
@@ -70403,7 +70403,7 @@
       </c>
       <c r="AJ373" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK373" t="inlineStr">
@@ -70778,7 +70778,7 @@
       </c>
       <c r="AJ375" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK375" t="inlineStr">
@@ -71153,7 +71153,7 @@
       </c>
       <c r="AJ377" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK377" t="inlineStr">
@@ -71528,7 +71528,7 @@
       </c>
       <c r="AJ379" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK379" t="inlineStr">
@@ -71903,7 +71903,7 @@
       </c>
       <c r="AJ381" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK381" t="inlineStr">
@@ -72278,7 +72278,7 @@
       </c>
       <c r="AJ383" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK383" t="inlineStr">
@@ -72662,7 +72662,7 @@
       </c>
       <c r="AJ385" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK385" t="inlineStr">
@@ -73046,7 +73046,7 @@
       </c>
       <c r="AJ387" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK387" t="inlineStr">
@@ -73421,7 +73421,7 @@
       </c>
       <c r="AJ389" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK389" t="inlineStr">
@@ -73796,7 +73796,7 @@
       </c>
       <c r="AJ391" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK391" t="inlineStr">
@@ -74171,7 +74171,7 @@
       </c>
       <c r="AJ393" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK393" t="inlineStr">
@@ -74546,7 +74546,7 @@
       </c>
       <c r="AJ395" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK395" t="inlineStr">
@@ -74921,7 +74921,7 @@
       </c>
       <c r="AJ397" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK397" t="inlineStr">
@@ -75296,7 +75296,7 @@
       </c>
       <c r="AJ399" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK399" t="inlineStr">
@@ -75671,7 +75671,7 @@
       </c>
       <c r="AJ401" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK401" t="inlineStr">
@@ -76046,7 +76046,7 @@
       </c>
       <c r="AJ403" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK403" t="inlineStr">
@@ -76421,7 +76421,7 @@
       </c>
       <c r="AJ405" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK405" t="inlineStr">
@@ -76796,7 +76796,7 @@
       </c>
       <c r="AJ407" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK407" t="inlineStr">
@@ -77171,7 +77171,7 @@
       </c>
       <c r="AJ409" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK409" t="inlineStr">
@@ -77546,7 +77546,7 @@
       </c>
       <c r="AJ411" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK411" t="inlineStr">
@@ -77921,7 +77921,7 @@
       </c>
       <c r="AJ413" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK413" t="inlineStr">
@@ -78296,7 +78296,7 @@
       </c>
       <c r="AJ415" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK415" t="inlineStr">
@@ -78671,7 +78671,7 @@
       </c>
       <c r="AJ417" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK417" t="inlineStr">
@@ -79046,7 +79046,7 @@
       </c>
       <c r="AJ419" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK419" t="inlineStr">
@@ -79421,7 +79421,7 @@
       </c>
       <c r="AJ421" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK421" t="inlineStr">
@@ -79796,7 +79796,7 @@
       </c>
       <c r="AJ423" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK423" t="inlineStr">
@@ -80171,7 +80171,7 @@
       </c>
       <c r="AJ425" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK425" t="inlineStr">
@@ -80546,7 +80546,7 @@
       </c>
       <c r="AJ427" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK427" t="inlineStr">
@@ -80921,7 +80921,7 @@
       </c>
       <c r="AJ429" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK429" t="inlineStr">
@@ -81296,7 +81296,7 @@
       </c>
       <c r="AJ431" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK431" t="inlineStr">
@@ -81671,7 +81671,7 @@
       </c>
       <c r="AJ433" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK433" t="inlineStr">
@@ -82046,7 +82046,7 @@
       </c>
       <c r="AJ435" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK435" t="inlineStr">
@@ -82421,7 +82421,7 @@
       </c>
       <c r="AJ437" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK437" t="inlineStr">
@@ -82796,7 +82796,7 @@
       </c>
       <c r="AJ439" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK439" t="inlineStr">
